--- a/public/assets/documents/excel/sample_upload/Topic.xlsx
+++ b/public/assets/documents/excel/sample_upload/Topic.xlsx
@@ -24,12 +24,6 @@
   </si>
   <si>
     <t>Topic Name</t>
-  </si>
-  <si>
-    <t>Type One Topic</t>
-  </si>
-  <si>
-    <t>Type Two Topic</t>
   </si>
 </sst>
 </file>
@@ -347,28 +341,14 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1"/>
-      <c r="D1"/>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2"/>
-      <c r="D2"/>
+      <c r="A2"/>
+      <c r="B2"/>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3"/>
-      <c r="D3"/>
+      <c r="A3"/>
+      <c r="B3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
